--- a/static/Requests.xlsx
+++ b/static/Requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarsitihanaf\Desktop\PROJECT\BE_DEV_DAHSBOARD\Dashboard\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8942C183-5EF1-40AF-A2AE-875E2212AC4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345A0B8E-086A-493C-BD85-BE58E0CE6CED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>No</t>
   </si>
@@ -68,6 +68,45 @@
   </si>
   <si>
     <t>Admin Comments</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>Sarsitihanaf</t>
+  </si>
+  <si>
+    <t>sitihanafinilam.sari@infineon.com</t>
+  </si>
+  <si>
+    <t>Innovation</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>27/04/2026 15:10</t>
+  </si>
+  <si>
+    <t>PLA</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>27/04/2026 15:10:07</t>
+  </si>
+  <si>
+    <t>[{"Status": "Review Drawing", "Date": "27/04/26 15:08"}, {"Status": "3D drawing processing", "Date": "27/04/26 15:09", "Admin Comments": ""}, {"Status": "Completed", "Date": "27/04/26 15:10", "Admin Comments": ""}]</t>
   </si>
 </sst>
 </file>
@@ -407,8 +446,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="186.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -458,6 +515,50 @@
       </c>
       <c r="P1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
